--- a/tools/bsi/bsi-c5-2020.xlsx
+++ b/tools/bsi/bsi-c5-2020.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abder/mydev/intuitem/staging/ciso-assistant-community/tools/bsi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3457778F-4FB1-6A4D-A640-AD90559DC9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DDFF5C-F719-8B4B-A9FA-75340BFE8664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="-23980" windowWidth="34560" windowHeight="20480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11460" yWindow="-23980" windowWidth="34560" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_content" sheetId="1" r:id="rId1"/>
@@ -1418,9 +1418,6 @@
   </si>
   <si>
     <t>BSI-C5-2020</t>
-  </si>
-  <si>
-    <t>Criteria Catalogue C5</t>
   </si>
   <si>
     <t>Organisation of Information Security (OIS)</t>
@@ -2101,6 +2098,9 @@
   <si>
     <t>This criterion supplements the General Condition BC-01.
 The cloud architecture must exist in such a way that it enables the technical design of the IT infrastructure to provide the cloud service in accordance with the data location specifications agreed with the customer.</t>
+  </si>
+  <si>
+    <t>Cloud Computing Compliance Criteria Catalogue (C5)</t>
   </si>
 </sst>
 </file>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2546,7 +2546,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>373</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2570,7 +2570,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2578,7 +2578,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2602,7 +2602,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>373</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2666,7 +2666,7 @@
         <v>24</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.2">
@@ -2688,13 +2688,13 @@
         <v>145</v>
       </c>
       <c r="D3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>264</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="160" x14ac:dyDescent="0.2">
@@ -2714,7 +2714,7 @@
         <v>265</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="192" x14ac:dyDescent="0.2">
@@ -2734,7 +2734,7 @@
         <v>266</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="176" x14ac:dyDescent="0.2">
@@ -2754,7 +2754,7 @@
         <v>267</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="160" x14ac:dyDescent="0.2">
@@ -2774,7 +2774,7 @@
         <v>268</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="176" x14ac:dyDescent="0.2">
@@ -2794,7 +2794,7 @@
         <v>269</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="208" x14ac:dyDescent="0.2">
@@ -2811,10 +2811,10 @@
         <v>31</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>402</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -2822,7 +2822,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
@@ -2842,7 +2842,7 @@
         <v>270</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="144" x14ac:dyDescent="0.2">
@@ -2879,7 +2879,7 @@
         <v>272</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -2887,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="256" x14ac:dyDescent="0.2">
@@ -2907,7 +2907,7 @@
         <v>273</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -2927,7 +2927,7 @@
         <v>274</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="160" x14ac:dyDescent="0.2">
@@ -2947,7 +2947,7 @@
         <v>275</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="144" x14ac:dyDescent="0.2">
@@ -2967,7 +2967,7 @@
         <v>276</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -2984,10 +2984,10 @@
         <v>39</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="240" x14ac:dyDescent="0.2">
@@ -3007,7 +3007,7 @@
         <v>277</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -3015,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="395" x14ac:dyDescent="0.2">
@@ -3035,7 +3035,7 @@
         <v>278</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="395" x14ac:dyDescent="0.2">
@@ -3072,7 +3072,7 @@
         <v>280</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3092,7 +3092,7 @@
         <v>281</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -3112,7 +3112,7 @@
         <v>282</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3129,10 +3129,10 @@
         <v>46</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="380" x14ac:dyDescent="0.2">
@@ -3160,7 +3160,7 @@
         <v>283</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="160" x14ac:dyDescent="0.2">
@@ -3180,7 +3180,7 @@
         <v>284</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="112" x14ac:dyDescent="0.2">
@@ -3197,10 +3197,10 @@
         <v>49</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>419</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="272" x14ac:dyDescent="0.2">
@@ -3228,7 +3228,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D33" t="s">
         <v>51</v>
@@ -3237,7 +3237,7 @@
         <v>286</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="335" x14ac:dyDescent="0.2">
@@ -3257,7 +3257,7 @@
         <v>287</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -3277,7 +3277,7 @@
         <v>288</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -3285,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="112" x14ac:dyDescent="0.2">
@@ -3305,7 +3305,7 @@
         <v>289</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="160" x14ac:dyDescent="0.2">
@@ -3325,7 +3325,7 @@
         <v>290</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="176" x14ac:dyDescent="0.2">
@@ -3345,7 +3345,7 @@
         <v>291</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="112" x14ac:dyDescent="0.2">
@@ -3362,10 +3362,10 @@
         <v>57</v>
       </c>
       <c r="E40" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -3385,7 +3385,7 @@
         <v>292</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="144" x14ac:dyDescent="0.2">
@@ -3405,7 +3405,7 @@
         <v>293</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -3425,7 +3425,7 @@
         <v>294</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -3445,7 +3445,7 @@
         <v>295</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3465,7 +3465,7 @@
         <v>296</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="208" x14ac:dyDescent="0.2">
@@ -3485,7 +3485,7 @@
         <v>297</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="208" x14ac:dyDescent="0.2">
@@ -3505,7 +3505,7 @@
         <v>298</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="112" x14ac:dyDescent="0.2">
@@ -3522,7 +3522,7 @@
         <v>65</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3559,7 +3559,7 @@
         <v>300</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3579,7 +3579,7 @@
         <v>301</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -3599,7 +3599,7 @@
         <v>302</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -3619,7 +3619,7 @@
         <v>303</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="160" x14ac:dyDescent="0.2">
@@ -3639,7 +3639,7 @@
         <v>304</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="176" x14ac:dyDescent="0.2">
@@ -3659,7 +3659,7 @@
         <v>305</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3679,7 +3679,7 @@
         <v>306</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3716,7 +3716,7 @@
         <v>308</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="224" x14ac:dyDescent="0.2">
@@ -3736,7 +3736,7 @@
         <v>309</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3756,7 +3756,7 @@
         <v>310</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
@@ -3764,7 +3764,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="350" x14ac:dyDescent="0.2">
@@ -3784,7 +3784,7 @@
         <v>311</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -3804,7 +3804,7 @@
         <v>312</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -3824,7 +3824,7 @@
         <v>313</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -3844,7 +3844,7 @@
         <v>314</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3864,7 +3864,7 @@
         <v>315</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="96" x14ac:dyDescent="0.2">
@@ -3884,7 +3884,7 @@
         <v>316</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -3904,7 +3904,7 @@
         <v>317</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="192" x14ac:dyDescent="0.2">
@@ -3921,10 +3921,10 @@
         <v>85</v>
       </c>
       <c r="E69" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -3944,7 +3944,7 @@
         <v>318</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
@@ -3952,7 +3952,7 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="144" x14ac:dyDescent="0.2">
@@ -3969,10 +3969,10 @@
         <v>87</v>
       </c>
       <c r="E72" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="96" x14ac:dyDescent="0.2">
@@ -3992,7 +3992,7 @@
         <v>319</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -4012,7 +4012,7 @@
         <v>320</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="272" x14ac:dyDescent="0.2">
@@ -4032,7 +4032,7 @@
         <v>321</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
@@ -4040,7 +4040,7 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -4060,7 +4060,7 @@
         <v>322</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="176" x14ac:dyDescent="0.2">
@@ -4080,7 +4080,7 @@
         <v>323</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="128" x14ac:dyDescent="0.2">
@@ -4100,7 +4100,7 @@
         <v>324</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -4120,7 +4120,7 @@
         <v>325</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -4157,7 +4157,7 @@
         <v>327</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -4177,7 +4177,7 @@
         <v>328</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -4194,10 +4194,10 @@
         <v>98</v>
       </c>
       <c r="E84" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="F84" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
@@ -4205,7 +4205,7 @@
         <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="80" x14ac:dyDescent="0.2">
@@ -4242,7 +4242,7 @@
         <v>330</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="80" x14ac:dyDescent="0.2">
@@ -4262,7 +4262,7 @@
         <v>331</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
@@ -4270,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="144" x14ac:dyDescent="0.2">
@@ -4284,13 +4284,13 @@
         <v>221</v>
       </c>
       <c r="D90" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>332</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="112" x14ac:dyDescent="0.2">
@@ -4310,7 +4310,7 @@
         <v>333</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="224" x14ac:dyDescent="0.2">
@@ -4330,7 +4330,7 @@
         <v>334</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -4367,7 +4367,7 @@
         <v>336</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="80" x14ac:dyDescent="0.2">
@@ -4387,7 +4387,7 @@
         <v>337</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -4424,7 +4424,7 @@
         <v>339</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -4444,7 +4444,7 @@
         <v>340</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -4469,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="304" x14ac:dyDescent="0.2">
@@ -4489,7 +4489,7 @@
         <v>342</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="160" x14ac:dyDescent="0.2">
@@ -4526,7 +4526,7 @@
         <v>344</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="350" x14ac:dyDescent="0.2">
@@ -4546,7 +4546,7 @@
         <v>345</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="272" x14ac:dyDescent="0.2">
@@ -4563,10 +4563,10 @@
         <v>115</v>
       </c>
       <c r="E105" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="F105" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
@@ -4574,7 +4574,7 @@
         <v>1</v>
       </c>
       <c r="C106" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="112" x14ac:dyDescent="0.2">
@@ -4594,7 +4594,7 @@
         <v>346</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -4614,7 +4614,7 @@
         <v>347</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="80" x14ac:dyDescent="0.2">
@@ -4634,7 +4634,7 @@
         <v>348</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -4671,7 +4671,7 @@
         <v>350</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
@@ -4679,7 +4679,7 @@
         <v>1</v>
       </c>
       <c r="C112" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -4716,7 +4716,7 @@
         <v>352</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="304" x14ac:dyDescent="0.2">
@@ -4736,7 +4736,7 @@
         <v>353</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
@@ -4756,7 +4756,7 @@
         <v>354</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="C117" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="176" x14ac:dyDescent="0.2">
@@ -4784,7 +4784,7 @@
         <v>355</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="112" x14ac:dyDescent="0.2">
@@ -4804,7 +4804,7 @@
         <v>356</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="256" x14ac:dyDescent="0.2">
@@ -4821,10 +4821,10 @@
         <v>127</v>
       </c>
       <c r="E120" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="F120" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -4844,7 +4844,7 @@
         <v>357</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
@@ -4852,7 +4852,7 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -4880,7 +4880,7 @@
         <v>2</v>
       </c>
       <c r="C124" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D124" t="s">
         <v>130</v>
@@ -4889,7 +4889,7 @@
         <v>359</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -4923,7 +4923,7 @@
         <v>132</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
@@ -4931,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="C127" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="320" x14ac:dyDescent="0.2">
@@ -4948,7 +4948,7 @@
         <v>133</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="208" x14ac:dyDescent="0.2">
@@ -4968,7 +4968,7 @@
         <v>361</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="112" x14ac:dyDescent="0.2">
@@ -4988,7 +4988,7 @@
         <v>362</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="208" x14ac:dyDescent="0.2">
@@ -5008,7 +5008,7 @@
         <v>363</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="96" x14ac:dyDescent="0.2">
@@ -5028,7 +5028,7 @@
         <v>364</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="32" x14ac:dyDescent="0.2">
@@ -5048,7 +5048,7 @@
         <v>365</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="144" x14ac:dyDescent="0.2">
@@ -5068,7 +5068,7 @@
         <v>366</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="128" x14ac:dyDescent="0.2">
@@ -5088,7 +5088,7 @@
         <v>367</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -5108,7 +5108,7 @@
         <v>368</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -5128,7 +5128,7 @@
         <v>369</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="112" x14ac:dyDescent="0.2">
@@ -5148,7 +5148,7 @@
         <v>370</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="48" x14ac:dyDescent="0.2">
@@ -5168,7 +5168,7 @@
         <v>371</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
